--- a/www/flightdata/xlsx/eoss-367.xlsx
+++ b/www/flightdata/xlsx/eoss-367.xlsx
@@ -2673,7 +2673,7 @@
         <v>27201.88</v>
       </c>
       <c r="I2">
-        <v>471</v>
+        <v>309</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
